--- a/research/traditional_assets/database/data/kenya/kenya_trucking.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_trucking.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-1.649193548387097</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-1.649193548387097</v>
       </c>
       <c r="I2">
-        <v>-1.819587628865979</v>
+        <v>-2.705645161290323</v>
       </c>
       <c r="J2">
-        <v>-1.819587628865979</v>
+        <v>-2.705645161290323</v>
       </c>
       <c r="K2">
-        <v>-0.41</v>
+        <v>-0.702</v>
       </c>
       <c r="L2">
-        <v>-2.11340206185567</v>
+        <v>-2.830645161290323</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,67 +627,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="V2">
-        <v>0.001734104046242775</v>
+        <v>0.003296703296703297</v>
       </c>
       <c r="W2">
-        <v>-2.469879518072289</v>
+        <v>-0.1251336898395722</v>
       </c>
       <c r="X2">
-        <v>0.1975479916524256</v>
+        <v>0.2770096875264229</v>
       </c>
       <c r="Y2">
-        <v>-2.667427509724714</v>
+        <v>-0.402143377365995</v>
       </c>
       <c r="Z2">
-        <v>0.06598639455782314</v>
+        <v>0.02981844415053505</v>
       </c>
       <c r="AA2">
-        <v>-0.1200680272108843</v>
+        <v>-0.08067812913310088</v>
       </c>
       <c r="AB2">
-        <v>0.1089260256065659</v>
+        <v>0.168353586941297</v>
       </c>
       <c r="AC2">
-        <v>-0.2289940528174503</v>
+        <v>-0.2490317160743978</v>
       </c>
       <c r="AD2">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="AG2">
-        <v>2.707</v>
+        <v>2.384</v>
       </c>
       <c r="AH2">
-        <v>0.6103603603603605</v>
+        <v>0.5676959619952494</v>
       </c>
       <c r="AI2">
-        <v>0.3257211538461539</v>
+        <v>0.3504398826979472</v>
       </c>
       <c r="AJ2">
-        <v>0.6100969123281497</v>
+        <v>0.5670789724072312</v>
       </c>
       <c r="AK2">
-        <v>0.3254779367560418</v>
+        <v>0.3498679189903141</v>
       </c>
       <c r="AL2">
-        <v>0.103</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.103</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AO2">
-        <v>-3.427184466019417</v>
+        <v>-9.450704225352114</v>
       </c>
       <c r="AQ2">
-        <v>-3.427184466019417</v>
+        <v>-9.450704225352114</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +707,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-1.649193548387097</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-1.649193548387097</v>
       </c>
       <c r="I3">
-        <v>-1.819587628865979</v>
+        <v>-2.705645161290323</v>
       </c>
       <c r="J3">
-        <v>-1.819587628865979</v>
+        <v>-2.705645161290323</v>
       </c>
       <c r="K3">
-        <v>-0.41</v>
+        <v>-0.702</v>
       </c>
       <c r="L3">
-        <v>-2.11340206185567</v>
+        <v>-2.830645161290323</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +746,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="V3">
-        <v>0.001734104046242775</v>
+        <v>0.003296703296703297</v>
       </c>
       <c r="W3">
-        <v>-2.469879518072289</v>
+        <v>-0.1251336898395722</v>
       </c>
       <c r="X3">
-        <v>0.1975479916524256</v>
+        <v>0.2770096875264229</v>
       </c>
       <c r="Y3">
-        <v>-2.667427509724714</v>
+        <v>-0.402143377365995</v>
       </c>
       <c r="Z3">
-        <v>0.06598639455782314</v>
+        <v>0.02981844415053505</v>
       </c>
       <c r="AA3">
-        <v>-0.1200680272108843</v>
+        <v>-0.08067812913310088</v>
       </c>
       <c r="AB3">
-        <v>0.1089260256065659</v>
+        <v>0.168353586941297</v>
       </c>
       <c r="AC3">
-        <v>-0.2289940528174503</v>
+        <v>-0.2490317160743978</v>
       </c>
       <c r="AD3">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="AG3">
-        <v>2.707</v>
+        <v>2.384</v>
       </c>
       <c r="AH3">
-        <v>0.6103603603603605</v>
+        <v>0.5676959619952494</v>
       </c>
       <c r="AI3">
-        <v>0.3257211538461539</v>
+        <v>0.3504398826979472</v>
       </c>
       <c r="AJ3">
-        <v>0.6100969123281497</v>
+        <v>0.5670789724072312</v>
       </c>
       <c r="AK3">
-        <v>0.3254779367560418</v>
+        <v>0.3498679189903141</v>
       </c>
       <c r="AL3">
-        <v>0.103</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM3">
-        <v>0.103</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AO3">
-        <v>-3.427184466019417</v>
+        <v>-9.450704225352114</v>
       </c>
       <c r="AQ3">
-        <v>-3.427184466019417</v>
+        <v>-9.450704225352114</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kenya/kenya_trucking.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_trucking.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-1.649193548387097</v>
+        <v>-1.737864077669903</v>
       </c>
       <c r="H2">
-        <v>-1.649193548387097</v>
+        <v>-1.737864077669903</v>
       </c>
       <c r="I2">
-        <v>-2.705645161290323</v>
+        <v>-2.830097087378641</v>
       </c>
       <c r="J2">
-        <v>-2.705645161290323</v>
+        <v>-2.830097087378641</v>
       </c>
       <c r="K2">
-        <v>-0.702</v>
+        <v>-0.644</v>
       </c>
       <c r="L2">
-        <v>-2.830645161290323</v>
+        <v>-3.12621359223301</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,67 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.003296703296703297</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-0.1251336898395722</v>
+        <v>-0.145372460496614</v>
       </c>
       <c r="X2">
-        <v>0.2770096875264229</v>
+        <v>0.1625114380762863</v>
       </c>
       <c r="Y2">
-        <v>-0.402143377365995</v>
+        <v>-0.3078838985729003</v>
       </c>
       <c r="Z2">
-        <v>0.02981844415053505</v>
+        <v>0.03023187555033754</v>
       </c>
       <c r="AA2">
-        <v>-0.08067812913310088</v>
+        <v>-0.08555914294100381</v>
       </c>
       <c r="AB2">
-        <v>0.168353586941297</v>
+        <v>0.1564549151309767</v>
       </c>
       <c r="AC2">
-        <v>-0.2490317160743978</v>
+        <v>-0.2420140580719805</v>
       </c>
       <c r="AD2">
-        <v>2.39</v>
+        <v>0.096</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.39</v>
+        <v>0.096</v>
       </c>
       <c r="AG2">
-        <v>2.384</v>
+        <v>0.096</v>
       </c>
       <c r="AH2">
-        <v>0.5676959619952494</v>
+        <v>0.07830342577487766</v>
       </c>
       <c r="AI2">
-        <v>0.3504398826979472</v>
+        <v>0.02245088868101029</v>
       </c>
       <c r="AJ2">
-        <v>0.5670789724072312</v>
+        <v>0.07830342577487766</v>
       </c>
       <c r="AK2">
-        <v>0.3498679189903141</v>
+        <v>0.02245088868101029</v>
       </c>
       <c r="AL2">
-        <v>0.07099999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="AM2">
-        <v>0.07099999999999999</v>
+        <v>0.231</v>
+      </c>
+      <c r="AN2">
+        <v>-0.237037037037037</v>
       </c>
       <c r="AO2">
-        <v>-9.450704225352114</v>
+        <v>-2.523809523809524</v>
+      </c>
+      <c r="AP2">
+        <v>-0.237037037037037</v>
       </c>
       <c r="AQ2">
-        <v>-9.450704225352114</v>
+        <v>-2.523809523809524</v>
       </c>
     </row>
     <row r="3">
@@ -707,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-1.649193548387097</v>
+        <v>-1.737864077669903</v>
       </c>
       <c r="H3">
-        <v>-1.649193548387097</v>
+        <v>-1.737864077669903</v>
       </c>
       <c r="I3">
-        <v>-2.705645161290323</v>
+        <v>-2.830097087378641</v>
       </c>
       <c r="J3">
-        <v>-2.705645161290323</v>
+        <v>-2.830097087378641</v>
       </c>
       <c r="K3">
-        <v>-0.702</v>
+        <v>-0.644</v>
       </c>
       <c r="L3">
-        <v>-2.830645161290323</v>
+        <v>-3.12621359223301</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.003296703296703297</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.1251336898395722</v>
+        <v>-0.145372460496614</v>
       </c>
       <c r="X3">
-        <v>0.2770096875264229</v>
+        <v>0.1625114380762863</v>
       </c>
       <c r="Y3">
-        <v>-0.402143377365995</v>
+        <v>-0.3078838985729003</v>
       </c>
       <c r="Z3">
-        <v>0.02981844415053505</v>
+        <v>0.03023187555033754</v>
       </c>
       <c r="AA3">
-        <v>-0.08067812913310088</v>
+        <v>-0.08555914294100381</v>
       </c>
       <c r="AB3">
-        <v>0.168353586941297</v>
+        <v>0.1564549151309767</v>
       </c>
       <c r="AC3">
-        <v>-0.2490317160743978</v>
+        <v>-0.2420140580719805</v>
       </c>
       <c r="AD3">
-        <v>2.39</v>
+        <v>0.096</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.39</v>
+        <v>0.096</v>
       </c>
       <c r="AG3">
-        <v>2.384</v>
+        <v>0.096</v>
       </c>
       <c r="AH3">
-        <v>0.5676959619952494</v>
+        <v>0.07830342577487766</v>
       </c>
       <c r="AI3">
-        <v>0.3504398826979472</v>
+        <v>0.02245088868101029</v>
       </c>
       <c r="AJ3">
-        <v>0.5670789724072312</v>
+        <v>0.07830342577487766</v>
       </c>
       <c r="AK3">
-        <v>0.3498679189903141</v>
+        <v>0.02245088868101029</v>
       </c>
       <c r="AL3">
-        <v>0.07099999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="AM3">
-        <v>0.07099999999999999</v>
+        <v>0.231</v>
+      </c>
+      <c r="AN3">
+        <v>-0.237037037037037</v>
       </c>
       <c r="AO3">
-        <v>-9.450704225352114</v>
+        <v>-2.523809523809524</v>
+      </c>
+      <c r="AP3">
+        <v>-0.237037037037037</v>
       </c>
       <c r="AQ3">
-        <v>-9.450704225352114</v>
+        <v>-2.523809523809524</v>
       </c>
     </row>
   </sheetData>
